--- a/ai_logs/HoangCau_AI_log.xlsx
+++ b/ai_logs/HoangCau_AI_log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2.1\run\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2.1\SE20C2_LeHoangCau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E10106C-AB03-4A82-9878-89397270FAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A673485-4B39-402B-99B9-FB33BBF733C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1032" windowWidth="21600" windowHeight="11208" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="233">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Total Prompts Used (all AI tools):</t>
   </si>
   <si>
-    <t>~50</t>
-  </si>
-  <si>
     <t>Core Prompts Logged:</t>
   </si>
   <si>
@@ -95,24 +92,9 @@
     <t>High</t>
   </si>
   <si>
-    <t>DeepSeek</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>NotebookLM</t>
-  </si>
-  <si>
-    <t>Document synthesis, report generation</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Summarize project docs</t>
-  </si>
-  <si>
     <t>[Add more...]</t>
   </si>
   <si>
@@ -206,9 +188,6 @@
     <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
   </si>
   <si>
-    <t>☐</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -299,21 +278,12 @@
     <t>E-Commerce Flash Sale Simulation</t>
   </si>
   <si>
-    <t>Designing the database and synchronizing the storage system.</t>
-  </si>
-  <si>
-    <t>Analyze the advantages and disadvantages of each mechanism.</t>
-  </si>
-  <si>
     <t>ChatGPT</t>
   </si>
   <si>
     <t>Repository Design, Lock Mechanisms, Custom Exceptions</t>
   </si>
   <si>
-    <t>Compare Synchronization Algorithms</t>
-  </si>
-  <si>
     <t>Context Mismatch</t>
   </si>
   <si>
@@ -387,6 +357,394 @@
   </si>
   <si>
     <t>Added the missing import org.junit.Test; line to the test file. Also fixed the deprecated warning on assertEquals for double values by adding a delta tolerance of 0.001.</t>
+  </si>
+  <si>
+    <t>~55</t>
+  </si>
+  <si>
+    <t>Requirement analysis, design review</t>
+  </si>
+  <si>
+    <t>Auto-completion</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>GitHub Copilot</t>
+  </si>
+  <si>
+    <t>Helped implement features, debug Java code, generate unit tests, and prepare documentation</t>
+  </si>
+  <si>
+    <t>Deep reflection</t>
+  </si>
+  <si>
+    <t>Speed up coding</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>Có (quyết định thuật toán Lock)</t>
+  </si>
+  <si>
+    <t>Có, code sẽ thiếu cơ chế đồng bộ</t>
+  </si>
+  <si>
+    <t>Có, dựa trên hiệu năng thực tế</t>
+  </si>
+  <si>
+    <t>Có (Log file, test result)</t>
+  </si>
+  <si>
+    <t>Có (đã check/debug lại AI)</t>
+  </si>
+  <si>
+    <t>12-15 entries</t>
+  </si>
+  <si>
+    <t>Đã có đủ (Comp/Recog/Abstr/Alg)</t>
+  </si>
+  <si>
+    <t>Trên 5-10 loại</t>
+  </si>
+  <si>
+    <t>Đã có đầy đủ</t>
+  </si>
+  <si>
+    <t>Đã đính kèm ảnh/log</t>
+  </si>
+  <si>
+    <t>Tối ưu hóa hiệu năng bằng cách so sánh No Lock và Khả năng Optimistic Lock dưới các yêu cầu đồng thời.</t>
+  </si>
+  <si>
+    <t>Đảm bảo tính nhất quán của dữ liệu bằng cách triển khai OrderRepository cho việc lưu trữ đơn hàng.</t>
+  </si>
+  <si>
+    <t>Tối ưu hóa hiệu năng bằng Optimistic Lock trong Flash Sale</t>
+  </si>
+  <si>
+    <t>Có</t>
+  </si>
+  <si>
+    <t>FlashSaleItemRepository.java + benchmark.log</t>
+  </si>
+  <si>
+    <t>OrderRepository.java + orders.csv</t>
+  </si>
+  <si>
+    <t>FlashSaleItemRepository.java + transaction.log</t>
+  </si>
+  <si>
+    <t>Incorrect API Suggestion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Suggested using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>LockMechanism.REENTRANT_LOCK</t>
+    </r>
+  </si>
+  <si>
+    <t>The project's LockMechanism enum only contains NO_LOCK, SYNCHRONIZED, FILE_LOCK, and OPTIMISTIC_LOCK.</t>
+  </si>
+  <si>
+    <t>Verified the actual enum source code.</t>
+  </si>
+  <si>
+    <t>Replaced the invalid enum value with a valid one (FILE_LOCK or SYNCHRONIZED).</t>
+  </si>
+  <si>
+    <t>Incorrect Output Expectation</t>
+  </si>
+  <si>
+    <t>Assumed toCsvLine() should output true.</t>
+  </si>
+  <si>
+    <t>The implementation actually outputs TRUE in uppercase.</t>
+  </si>
+  <si>
+    <t>Compared the Expected and Actual values in the JUnit Test Results.</t>
+  </si>
+  <si>
+    <t>Updated the expected test value (or modified the implementation if lowercase output was required).</t>
+  </si>
+  <si>
+    <t>Incorrect Environment Assumption</t>
+  </si>
+  <si>
+    <t>Assumed test failures were caused by missing CSV data files.</t>
+  </si>
+  <si>
+    <t>All required CSV files already existed in the project's data folder.</t>
+  </si>
+  <si>
+    <t>Verified the project structure and data directory.</t>
+  </si>
+  <si>
+    <t>Continued debugging the actual causes, including JDK configuration and JUnit settings.</t>
+  </si>
+  <si>
+    <t>Incorrect Code Generation</t>
+  </si>
+  <si>
+    <t>Generated OrderRepository, OrderDetailRepository, and OrderTransactionRepository using methods (findBy(), getHeader()).</t>
+  </si>
+  <si>
+    <t>The project's CsvRepository implementation did not support those methods.</t>
+  </si>
+  <si>
+    <t>Compilation errors in VS Code (findBy undefined, CsvRepository cannot be resolved).</t>
+  </si>
+  <si>
+    <t>Reviewed the project structure and rewrote the repositories according to the actual implementation.</t>
+  </si>
+  <si>
+    <t>Incorrect Project Assumption</t>
+  </si>
+  <si>
+    <t>Assumed repositories should be placed under repository package.</t>
+  </si>
+  <si>
+    <t>The new files were mistakenly created under src/test, causing package mismatch.</t>
+  </si>
+  <si>
+    <t>VS Code reported package repository does not match expected package test.</t>
+  </si>
+  <si>
+    <t>Moved repository classes into the correct src/repository package.</t>
+  </si>
+  <si>
+    <t>Incorrect Test Suite</t>
+  </si>
+  <si>
+    <t>Generated AllTests.java using JUnit 5 annotations (@Suite, @SelectClasses).</t>
+  </si>
+  <si>
+    <t>Project requires JUnit 4 @RunWith(Suite.class).</t>
+  </si>
+  <si>
+    <t>Compilation errors for org.junit.platform imports.</t>
+  </si>
+  <si>
+    <t>Replaced with JUnit 4 Suite annotations.</t>
+  </si>
+  <si>
+    <t>Invalid Enum Reference</t>
+  </si>
+  <si>
+    <t>Used LockMechanism.REENTRANT_LOCK in tests.</t>
+  </si>
+  <si>
+    <t>Actual enum values are NO_LOCK, SYNCHRONIZED, FILE_LOCK, and OPTIMISTIC_LOCK.</t>
+  </si>
+  <si>
+    <t>Compilation error: REENTRANT_LOCK cannot be resolved.</t>
+  </si>
+  <si>
+    <t>Updated test cases to use valid enum values.</t>
+  </si>
+  <si>
+    <t>Incomplete Validation</t>
+  </si>
+  <si>
+    <t>Suggested repository implementation without checking existing source files.</t>
+  </si>
+  <si>
+    <t>Actual project architecture differed from assumptions.</t>
+  </si>
+  <si>
+    <t>User shared source code for models and repository classes.</t>
+  </si>
+  <si>
+    <t>Regenerated solutions only after inspecting the real project files.</t>
+  </si>
+  <si>
+    <t>Flash Sale Concurrency</t>
+  </si>
+  <si>
+    <t>Implementation of various lock mechanisms (NoLock, Synchronized, FileLock, Optimistic).</t>
+  </si>
+  <si>
+    <t>Successful logical framework for FlashSaleItemRepository.</t>
+  </si>
+  <si>
+    <t>Code review and concurrency stress testing.</t>
+  </si>
+  <si>
+    <t>Refined lock logic to handle race conditions.</t>
+  </si>
+  <si>
+    <t>System Design</t>
+  </si>
+  <si>
+    <t>Comprehensive ERD design, schema, and database integrity rules.</t>
+  </si>
+  <si>
+    <t>Verified relational constraints and integrity logic.</t>
+  </si>
+  <si>
+    <t>System design walkthrough.</t>
+  </si>
+  <si>
+    <t>Adjusted terminology to industry standards.</t>
+  </si>
+  <si>
+    <t>Library Hallucination</t>
+  </si>
+  <si>
+    <t>API Hallucination</t>
+  </si>
+  <si>
+    <t>Environment Hallucination</t>
+  </si>
+  <si>
+    <t>Output Hallucination</t>
+  </si>
+  <si>
+    <t>Unsupported API Usage</t>
+  </si>
+  <si>
+    <t>Incorrect Enum</t>
+  </si>
+  <si>
+    <t>Wrong Package Structure</t>
+  </si>
+  <si>
+    <t>Premature Code Generation</t>
+  </si>
+  <si>
+    <t>Syntax Precision</t>
+  </si>
+  <si>
+    <t>Rendering Error</t>
+  </si>
+  <si>
+    <t>Recommended JUnit 5 for the project</t>
+  </si>
+  <si>
+    <t>Referenced the enum value REENTRANT_LOCK.</t>
+  </si>
+  <si>
+    <t>Suggested that missing data files caused the test failures.</t>
+  </si>
+  <si>
+    <t>Expected CSV output to contain true.</t>
+  </si>
+  <si>
+    <t>Assumed CsvRepository contained findBy() and related helper methods.</t>
+  </si>
+  <si>
+    <t>Used REENTRANT_LOCK</t>
+  </si>
+  <si>
+    <t>Suggested placing repository files in an incorrect package.</t>
+  </si>
+  <si>
+    <t>Produced repository code before reviewing project source.</t>
+  </si>
+  <si>
+    <t>FileLock behavior is universal across OS</t>
+  </si>
+  <si>
+    <t>LaTeX would render correctly in all presentation software</t>
+  </si>
+  <si>
+    <t>The assignment uses JUnit 4.13.2.</t>
+  </si>
+  <si>
+    <t>The enum value does not exist in the project.</t>
+  </si>
+  <si>
+    <t>The project already contained all required data files.</t>
+  </si>
+  <si>
+    <t>The implementation generated TRUE.</t>
+  </si>
+  <si>
+    <t>Those methods were unavailable in the project.</t>
+  </si>
+  <si>
+    <t>Enum definition did not contain that value.</t>
+  </si>
+  <si>
+    <t>Project package hierarchy was different.</t>
+  </si>
+  <si>
+    <t>Generated code did not compile.</t>
+  </si>
+  <si>
+    <t>FileLock implementation varies between Windows/Linux</t>
+  </si>
+  <si>
+    <t>Presentation software struggled with complex LaTeX syntax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked the project's dependencies and library files.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+  </si>
+  <si>
+    <t>Examined the LockMechanism.java source file.</t>
+  </si>
+  <si>
+    <t>Verified the project directory and file structure.</t>
+  </si>
+  <si>
+    <t>Observed the failed JUnit assertion comparing Expected vs. Actual output.</t>
+  </si>
+  <si>
+    <t>Java compiler errors</t>
+  </si>
+  <si>
+    <t>User shared LockMechanism.java.</t>
+  </si>
+  <si>
+    <t>VS Code package mismatch error.</t>
+  </si>
+  <si>
+    <t>Continuous compilation feedback from the user.</t>
+  </si>
+  <si>
+    <t>Java NIO documentation review</t>
+  </si>
+  <si>
+    <t>Visual inspection of slides</t>
+  </si>
+  <si>
+    <t>Converted all test classes to JUnit 4.</t>
+  </si>
+  <si>
+    <t>Used the correct enum values defined in the project.</t>
+  </si>
+  <si>
+    <t>Investigated the actual issue, which was related to the Java/JUnit environment.</t>
+  </si>
+  <si>
+    <t>Corrected the expected test result to match the implementation.</t>
+  </si>
+  <si>
+    <t>Adapted code to the real repository implementation.</t>
+  </si>
+  <si>
+    <t>Replaced with valid enum constants (FILE_LOCK or OPTIMISTIC_LOCK).</t>
+  </si>
+  <si>
+    <t>Followed the project's package structure exactly.</t>
+  </si>
+  <si>
+    <t>Requested project source before regenerating compatible code.</t>
+  </si>
+  <si>
+    <t>Added platform-specific environment warnings</t>
+  </si>
+  <si>
+    <t>Switched to Unicode/plain text for structural symbols</t>
   </si>
 </sst>
 </file>
@@ -396,7 +754,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,11 +770,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -424,7 +796,7 @@
       <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -432,99 +804,7 @@
       <sz val="14"/>
       <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -534,6 +814,103 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="7">
@@ -601,29 +978,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -632,16 +1009,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -651,48 +1025,89 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,14 +1396,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.6" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="3" spans="1:6" ht="18">
       <c r="A3" s="2" t="s">
@@ -996,23 +1411,23 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1020,11 +1435,11 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18">
@@ -1033,171 +1448,171 @@
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="17" t="s">
+      <c r="C11" s="18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="17" t="s">
+      <c r="C12" s="19">
+        <v>0.16</v>
+      </c>
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="20">
-        <v>0.16</v>
-      </c>
-      <c r="E12" s="21"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="19">
-        <v>2</v>
+      <c r="C13" s="18">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>21</v>
+      <c r="A19" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18">
       <c r="A22" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="22">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="B24" s="21">
+        <v>8</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="22">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="B25" s="21">
+        <v>4</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="22">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="B26" s="21">
+        <v>3</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="22">
-        <v>2</v>
+        <v>29</v>
+      </c>
+      <c r="B27" s="21">
+        <v>3</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1210,197 +1625,319 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="6" width="30" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="30" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+    </row>
+    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="31" t="s">
+      <c r="F3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="79.2" customHeight="1">
-      <c r="A4" s="16">
+    </row>
+    <row r="4" spans="1:8" ht="79.2" customHeight="1">
+      <c r="A4" s="32">
         <v>2</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" ht="70.2" customHeight="1">
+      <c r="A5" s="32">
+        <v>3</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="F5" s="33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60" customHeight="1">
+      <c r="A6" s="30">
+        <v>4</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="70.2" customHeight="1">
-      <c r="A5" s="16">
-        <v>3</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="13">
-        <v>4</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+    </row>
+    <row r="7" spans="1:8" ht="60" customHeight="1">
+      <c r="A7" s="30">
+        <v>5</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="60" customHeight="1">
+      <c r="A8" s="30">
+        <v>6</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="60" customHeight="1">
+      <c r="A9" s="30">
+        <v>7</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="60" customHeight="1">
+      <c r="A10" s="30">
+        <v>8</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="60" customHeight="1">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="60" customHeight="1">
+      <c r="A12" s="30">
+        <v>10</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="60" customHeight="1">
+      <c r="A13" s="30">
+        <v>11</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="60" customHeight="1">
+      <c r="A14" s="30">
+        <v>12</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="60" customHeight="1">
+      <c r="A15" s="30">
+        <v>13</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="60" customHeight="1">
+      <c r="A16" s="30">
+        <v>14</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1">
-      <c r="A17" s="13"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
@@ -1408,7 +1945,7 @@
       <c r="F17" s="13"/>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1">
-      <c r="A18" s="13"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -1416,7 +1953,7 @@
       <c r="F18" s="13"/>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1">
-      <c r="A19" s="13"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -1424,7 +1961,7 @@
       <c r="F19" s="13"/>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1">
-      <c r="A20" s="13"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -1432,7 +1969,7 @@
       <c r="F20" s="13"/>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1">
-      <c r="A21" s="13"/>
+      <c r="A21" s="30"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -1440,7 +1977,7 @@
       <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:6" ht="60" customHeight="1">
-      <c r="A22" s="13"/>
+      <c r="A22" s="30"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -1448,7 +1985,7 @@
       <c r="F22" s="13"/>
     </row>
     <row r="23" spans="1:6" ht="60" customHeight="1">
-      <c r="A23" s="13"/>
+      <c r="A23" s="30"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -1458,42 +1995,122 @@
     <row r="24" spans="1:6" ht="60" customHeight="1">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
+      <c r="C24" s="37"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
     </row>
+    <row r="25" spans="1:6">
+      <c r="B25" s="35"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="B26" s="35"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="B27" s="35"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="B28" s="35"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="B29" s="35"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+    </row>
     <row r="30" spans="1:6" ht="18">
       <c r="A30" s="2"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="11"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="13"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="13"/>
       <c r="B36" s="13"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1507,95 +2124,265 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" customWidth="1"/>
-    <col min="5" max="5" width="30.6640625" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="63.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.5546875" customWidth="1"/>
+    <col min="5" max="5" width="63" customWidth="1"/>
+    <col min="6" max="6" width="71.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="A1" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="A2" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:6" ht="28.8">
       <c r="A3" s="14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="103.8" customHeight="1">
       <c r="A4" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="80.099999999999994" customHeight="1">
+      <c r="B4" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="98.4" customHeight="1">
       <c r="A5" s="15">
         <v>2</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>116</v>
+      <c r="B5" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="34" customFormat="1">
+      <c r="B6" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -1613,285 +2400,285 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="60" style="1" customWidth="1"/>
+    <col min="2" max="2" width="60.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="A1" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="A2" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
     </row>
     <row r="4" spans="1:4" ht="18">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>26</v>
+        <v>115</v>
+      </c>
+      <c r="D8" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18">
       <c r="A12" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="8" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18">
       <c r="A25" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2">
       <c r="A27" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>70</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28.8">
       <c r="A28" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>74</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="27" customHeight="1">
       <c r="A29" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>75</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="28.8">
       <c r="A30" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>26</v>
+        <v>76</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/ai_logs/HoangCau_AI_log.xlsx
+++ b/ai_logs/HoangCau_AI_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2.1\SE20C2_LeHoangCau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A673485-4B39-402B-99B9-FB33BBF733C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669B6F00-2D7D-4C50-A89E-69FCE8D4B8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="223">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -582,21 +582,6 @@
     <t>Refined lock logic to handle race conditions.</t>
   </si>
   <si>
-    <t>System Design</t>
-  </si>
-  <si>
-    <t>Comprehensive ERD design, schema, and database integrity rules.</t>
-  </si>
-  <si>
-    <t>Verified relational constraints and integrity logic.</t>
-  </si>
-  <si>
-    <t>System design walkthrough.</t>
-  </si>
-  <si>
-    <t>Adjusted terminology to industry standards.</t>
-  </si>
-  <si>
     <t>Library Hallucination</t>
   </si>
   <si>
@@ -624,9 +609,6 @@
     <t>Syntax Precision</t>
   </si>
   <si>
-    <t>Rendering Error</t>
-  </si>
-  <si>
     <t>Recommended JUnit 5 for the project</t>
   </si>
   <si>
@@ -654,9 +636,6 @@
     <t>FileLock behavior is universal across OS</t>
   </si>
   <si>
-    <t>LaTeX would render correctly in all presentation software</t>
-  </si>
-  <si>
     <t>The assignment uses JUnit 4.13.2.</t>
   </si>
   <si>
@@ -684,9 +663,6 @@
     <t>FileLock implementation varies between Windows/Linux</t>
   </si>
   <si>
-    <t>Presentation software struggled with complex LaTeX syntax</t>
-  </si>
-  <si>
     <t xml:space="preserve">Checked the project's dependencies and library files.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
   </si>
   <si>
@@ -714,9 +690,6 @@
     <t>Java NIO documentation review</t>
   </si>
   <si>
-    <t>Visual inspection of slides</t>
-  </si>
-  <si>
     <t>Converted all test classes to JUnit 4.</t>
   </si>
   <si>
@@ -742,9 +715,6 @@
   </si>
   <si>
     <t>Added platform-specific environment warnings</t>
-  </si>
-  <si>
-    <t>Switched to Unicode/plain text for structural symbols</t>
   </si>
 </sst>
 </file>
@@ -754,12 +724,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -978,29 +955,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1009,13 +986,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1025,87 +1002,93 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1396,14 +1379,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.6" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="3" spans="1:6" ht="18">
       <c r="A3" s="2" t="s">
@@ -1636,24 +1619,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -1917,24 +1900,12 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" customHeight="1">
-      <c r="A16" s="30">
-        <v>14</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>182</v>
-      </c>
+      <c r="A16" s="30"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1">
       <c r="A17" s="30"/>
@@ -2124,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -2136,24 +2107,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
     </row>
     <row r="3" spans="1:6" ht="28.8">
       <c r="A3" s="14" t="s">
@@ -2216,173 +2187,156 @@
       </c>
     </row>
     <row r="6" spans="1:6" s="34" customFormat="1">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F7" s="39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.8">
+      <c r="B9" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" s="39" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C11" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="40" t="s">
         <v>193</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D12" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E13" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="F6" s="50" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>214</v>
-      </c>
-      <c r="F7" s="50" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>216</v>
-      </c>
-      <c r="F9" s="50" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="F10" s="50" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>208</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="F11" s="50" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="F13" s="50" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" s="51" t="s">
-        <v>211</v>
-      </c>
-      <c r="E14" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="F14" s="50" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="B15" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>212</v>
-      </c>
-      <c r="E15" s="51" t="s">
+      <c r="F14" s="39" t="s">
         <v>222</v>
-      </c>
-      <c r="F15" s="50" t="s">
-        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2407,20 +2361,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
     </row>
     <row r="4" spans="1:4" ht="18">
       <c r="A4" s="2" t="s">
